--- a/Alim400V.xlsx
+++ b/Alim400V.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a037702\NotSynchronized\git\Design_of_1200W_LLC_DCDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87DA3FC9-F1F6-4C2E-8CB9-B73D35442AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDB126A-3374-4DC6-9FD9-AB4C0DE13D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{61944083-4F3F-44B6-828A-7059F5989F4B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{61944083-4F3F-44B6-828A-7059F5989F4B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="DRAFT" sheetId="1" r:id="rId1"/>
+    <sheet name="ALIM1" sheetId="2" r:id="rId2"/>
+    <sheet name="ALIM2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
   <si>
     <t>R11</t>
   </si>
@@ -99,6 +99,30 @@
   <si>
     <t>R2paral</t>
   </si>
+  <si>
+    <t xml:space="preserve">REF </t>
+  </si>
+  <si>
+    <t>ADD POTO IN HEIGH</t>
+  </si>
+  <si>
+    <t>ADD POTO IN LOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rparal = </t>
+  </si>
+  <si>
+    <t>R2 equiv</t>
+  </si>
+  <si>
+    <t>Rpoten</t>
+  </si>
+  <si>
+    <t>Vout</t>
+  </si>
+  <si>
+    <t>measurement</t>
+  </si>
 </sst>
 </file>
 
@@ -119,12 +143,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -139,16 +175,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF66"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -215,7 +259,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$M$11</c:f>
+              <c:f>DRAFT!$M$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -250,7 +294,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$K$12:$K$22</c:f>
+              <c:f>DRAFT!$K$12:$K$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -280,7 +324,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$M$12:$M$22</c:f>
+              <c:f>DRAFT!$M$12:$M$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -557,7 +601,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sheet1 (2)'!$M$11</c:f>
+              <c:f>ALIM1!$M$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -592,7 +636,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'Sheet1 (2)'!$K$12:$K$22</c:f>
+              <c:f>ALIM1!$K$12:$K$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -619,7 +663,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Sheet1 (2)'!$M$12:$M$22</c:f>
+              <c:f>ALIM1!$M$12:$M$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -839,6 +883,330 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>ALIM2!$Q$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vout</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ALIM2!$R$19:$W$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ALIM2!$R$20:$W$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>342.7620360766058</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>353.61048026708244</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>365.2269070103863</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>377.69585926441846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>391.11476184090071</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>405.59647208583368</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0BC3-451E-BD7C-1412A01200E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1445805983"/>
+        <c:axId val="1445825663"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1445805983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1445825663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1445825663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1445805983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -919,6 +1287,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1436,6 +1844,522 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2030,6 +2954,91 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F007BF48-E7C3-C586-19CE-95CF5CD103C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>581167</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>124746</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2008BC95-728C-FFD5-947E-5259EDD1E35A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9052560" y="2301240"/>
+          <a:ext cx="14670547" cy="6601746"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3100,6 +4109,624 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5106018-94D2-4F77-8FE2-9594079986E8}">
+  <dimension ref="B1:W20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>680</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="L2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>27</v>
+      </c>
+      <c r="N2">
+        <v>27</v>
+      </c>
+      <c r="O2">
+        <v>27</v>
+      </c>
+      <c r="P2">
+        <v>27</v>
+      </c>
+      <c r="R2">
+        <v>27</v>
+      </c>
+      <c r="S2">
+        <v>27</v>
+      </c>
+      <c r="T2">
+        <v>27</v>
+      </c>
+      <c r="U2">
+        <v>27</v>
+      </c>
+      <c r="V2">
+        <v>27</v>
+      </c>
+      <c r="W2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <v>680</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>390</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="L3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>390</v>
+      </c>
+      <c r="N3">
+        <v>390</v>
+      </c>
+      <c r="O3">
+        <v>390</v>
+      </c>
+      <c r="P3">
+        <v>390</v>
+      </c>
+      <c r="R3">
+        <v>390</v>
+      </c>
+      <c r="S3">
+        <v>390</v>
+      </c>
+      <c r="T3">
+        <v>390</v>
+      </c>
+      <c r="U3">
+        <v>390</v>
+      </c>
+      <c r="V3">
+        <v>390</v>
+      </c>
+      <c r="W3">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>560</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <f>+F2*F3/(F2+F3)</f>
+        <v>25.25179856115108</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4">
+        <v>5</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>2</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2">
+        <f>+SUM(C2:C4)</f>
+        <v>1920</v>
+      </c>
+      <c r="L5" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5">
+        <f>+M2*M3/(M2+M3)</f>
+        <v>25.25179856115108</v>
+      </c>
+      <c r="N5">
+        <f>+M5</f>
+        <v>25.25179856115108</v>
+      </c>
+      <c r="O5">
+        <f>+M5+O4</f>
+        <v>30.25179856115108</v>
+      </c>
+      <c r="P5">
+        <f>+N5+P4</f>
+        <v>25.25179856115108</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:W5" si="0">+$P5+R4</f>
+        <v>30.25179856115108</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="0"/>
+        <v>29.25179856115108</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>28.25179856115108</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>27.25179856115108</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="0"/>
+        <v>26.25179856115108</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="0"/>
+        <v>25.25179856115108</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="L6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="2">
+        <f>+SUM(C2:C4)</f>
+        <v>1920</v>
+      </c>
+      <c r="N6" s="2">
+        <f>+M6+5</f>
+        <v>1925</v>
+      </c>
+      <c r="O6" s="2">
+        <f>+$M6</f>
+        <v>1920</v>
+      </c>
+      <c r="P6" s="2">
+        <f>+$M6</f>
+        <v>1920</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" ref="R6:W6" si="1">+$M6</f>
+        <v>1920</v>
+      </c>
+      <c r="S6" s="2">
+        <f t="shared" si="1"/>
+        <v>1920</v>
+      </c>
+      <c r="T6" s="2">
+        <f t="shared" si="1"/>
+        <v>1920</v>
+      </c>
+      <c r="U6" s="2">
+        <f t="shared" si="1"/>
+        <v>1920</v>
+      </c>
+      <c r="V6" s="2">
+        <f t="shared" si="1"/>
+        <v>1920</v>
+      </c>
+      <c r="W6" s="2">
+        <f t="shared" si="1"/>
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="7" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C7" s="2"/>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <f>+F4/(F4+C5)</f>
+        <v>1.2981249306557195E-2</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="N7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="3">
+        <v>470</v>
+      </c>
+      <c r="P7" s="4">
+        <v>470</v>
+      </c>
+      <c r="R7" s="3">
+        <v>470</v>
+      </c>
+      <c r="S7" s="3">
+        <v>470</v>
+      </c>
+      <c r="T7" s="3">
+        <v>470</v>
+      </c>
+      <c r="U7" s="3">
+        <v>470</v>
+      </c>
+      <c r="V7" s="3">
+        <v>470</v>
+      </c>
+      <c r="W7" s="3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C8" s="2"/>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>384</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="N8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8">
+        <f>+O5*O7/(O5+O7)</f>
+        <v>28.422377220104988</v>
+      </c>
+      <c r="P8">
+        <f>+P5*P7/(P5+P7)</f>
+        <v>23.964264962231265</v>
+      </c>
+      <c r="R8">
+        <f>+R5*R7/(R5+R7)</f>
+        <v>28.422377220104988</v>
+      </c>
+      <c r="S8">
+        <f>+S5*S7/(S5+S7)</f>
+        <v>27.537898437950318</v>
+      </c>
+      <c r="T8">
+        <f t="shared" ref="T8:V8" si="2">+T5*T7/(T5+T7)</f>
+        <v>26.649869327288219</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="2"/>
+        <v>25.758268468416333</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="2"/>
+        <v>24.863074268980416</v>
+      </c>
+      <c r="W8">
+        <f>+W5*W7/(W5+W7)</f>
+        <v>23.964264962231265</v>
+      </c>
+    </row>
+    <row r="9" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C9" s="2"/>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <f>+F8*F7</f>
+        <v>4.9847997337179626</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C10" s="2"/>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="K13" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13">
+        <f>+M5/(M5+M6)</f>
+        <v>1.2981249306557195E-2</v>
+      </c>
+      <c r="N13">
+        <f>+N5/(N5+N6)</f>
+        <v>1.2947968349410701E-2</v>
+      </c>
+      <c r="O13">
+        <f>+O8/(O8+O6)</f>
+        <v>1.4587379796292614E-2</v>
+      </c>
+      <c r="P13">
+        <f>+P8/(P8+P6)</f>
+        <v>1.232752339853164E-2</v>
+      </c>
+      <c r="R13">
+        <f>+R8/(R8+R6)</f>
+        <v>1.4587379796292614E-2</v>
+      </c>
+      <c r="S13">
+        <f>+S8/(S8+S6)</f>
+        <v>1.4139852405458949E-2</v>
+      </c>
+      <c r="T13">
+        <f t="shared" ref="T13:W13" si="3">+T8/(T8+T6)</f>
+        <v>1.3690119495653179E-2</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="3"/>
+        <v>1.3238164722636224E-2</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="3"/>
+        <v>1.2783971580274745E-2</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="3"/>
+        <v>1.232752339853164E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="K14" t="s">
+        <v>9</v>
+      </c>
+      <c r="M14">
+        <v>384</v>
+      </c>
+      <c r="N14">
+        <v>385</v>
+      </c>
+      <c r="O14">
+        <v>384</v>
+      </c>
+      <c r="P14">
+        <v>385</v>
+      </c>
+      <c r="R14">
+        <v>384</v>
+      </c>
+      <c r="S14">
+        <v>385</v>
+      </c>
+      <c r="T14">
+        <v>386</v>
+      </c>
+      <c r="U14">
+        <v>387</v>
+      </c>
+      <c r="V14">
+        <v>388</v>
+      </c>
+      <c r="W14">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15">
+        <f>+M14*M13</f>
+        <v>4.9847997337179626</v>
+      </c>
+      <c r="N15">
+        <f>+N14*N13</f>
+        <v>4.9849678145231202</v>
+      </c>
+      <c r="O15">
+        <f>+O14*O13</f>
+        <v>5.6015538417763642</v>
+      </c>
+      <c r="P15">
+        <f>+P14*P13</f>
+        <v>4.7460965084346816</v>
+      </c>
+      <c r="R15">
+        <f>+R14*R13</f>
+        <v>5.6015538417763642</v>
+      </c>
+      <c r="S15">
+        <f>+S14*S13</f>
+        <v>5.4438431761016952</v>
+      </c>
+      <c r="T15">
+        <f t="shared" ref="T15:W15" si="4">+T14*T13</f>
+        <v>5.2843861253221274</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="4"/>
+        <v>5.1231697476602189</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="4"/>
+        <v>4.9601809731466009</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="4"/>
+        <v>4.795406602028808</v>
+      </c>
+    </row>
+    <row r="16" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>11</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ref="M16:N16" si="5">5/M13</f>
+        <v>385.17094017094018</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="5"/>
+        <v>386.16096866096871</v>
+      </c>
+      <c r="O16" s="3">
+        <f>5/O13</f>
+        <v>342.7620360766058</v>
+      </c>
+      <c r="P16" s="3">
+        <f>5/P13</f>
+        <v>405.59647208583368</v>
+      </c>
+      <c r="R16" s="3">
+        <f>5/R13</f>
+        <v>342.7620360766058</v>
+      </c>
+      <c r="S16" s="3">
+        <f>5/S13</f>
+        <v>353.61048026708244</v>
+      </c>
+      <c r="T16" s="3">
+        <f t="shared" ref="T16:W16" si="6">5/T13</f>
+        <v>365.2269070103863</v>
+      </c>
+      <c r="U16" s="3">
+        <f t="shared" si="6"/>
+        <v>377.69585926441846</v>
+      </c>
+      <c r="V16" s="3">
+        <f t="shared" si="6"/>
+        <v>391.11476184090071</v>
+      </c>
+      <c r="W16" s="3">
+        <f t="shared" si="6"/>
+        <v>405.59647208583368</v>
+      </c>
+    </row>
+    <row r="17" spans="14:23" x14ac:dyDescent="0.3">
+      <c r="N17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="5">
+        <v>342.3</v>
+      </c>
+      <c r="P17" s="5">
+        <v>405.2</v>
+      </c>
+    </row>
+    <row r="19" spans="14:23" x14ac:dyDescent="0.3">
+      <c r="Q19" t="s">
+        <v>25</v>
+      </c>
+      <c r="R19">
+        <f>+R4</f>
+        <v>5</v>
+      </c>
+      <c r="S19">
+        <f t="shared" ref="S19:W19" si="7">+S4</f>
+        <v>4</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="14:23" x14ac:dyDescent="0.3">
+      <c r="Q20" t="s">
+        <v>26</v>
+      </c>
+      <c r="R20">
+        <f>+R16</f>
+        <v>342.7620360766058</v>
+      </c>
+      <c r="S20">
+        <f t="shared" ref="S20:W20" si="8">+S16</f>
+        <v>353.61048026708244</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="8"/>
+        <v>365.2269070103863</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="8"/>
+        <v>377.69585926441846</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="8"/>
+        <v>391.11476184090071</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="8"/>
+        <v>405.59647208583368</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{fd1c0902-ed92-4fed-896d-2e7725de02d4}" enabled="1" method="Standard" siteId="{d6b0bbee-7cd9-4d60-bce6-4a67b543e2ae}" contentBits="2" removed="0"/>
